--- a/data_entry.xlsx
+++ b/data_entry.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Интеграционное тестирование план</t>
+          <t>e2e план</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Интеграционное тестирование факт</t>
+          <t>e2e факт</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Интеграционное тестирование baseline</t>
+          <t>e2e baseline</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
